--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -434,15 +434,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -460,22 +470,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.01339</v>
+        <v>16.91693</v>
       </c>
       <c r="D2" t="n">
-        <v>16.26827</v>
+        <v>16.51763</v>
       </c>
       <c r="E2" t="n">
-        <v>17.04345</v>
+        <v>16.74233</v>
       </c>
       <c r="F2" t="n">
-        <v>42.79325</v>
+        <v>55.47303</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0509</v>
+        <v>43.09203</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81998</v>
+        <v>85.93447</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05111</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.83309</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +501,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.59032</v>
+        <v>16.66588</v>
       </c>
       <c r="D3" t="n">
-        <v>16.63385</v>
+        <v>16.45692</v>
       </c>
       <c r="E3" t="n">
-        <v>16.33329</v>
+        <v>16.65074</v>
       </c>
       <c r="F3" t="n">
-        <v>42.44136</v>
+        <v>55.85675</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05135</v>
+        <v>42.60559</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83321</v>
+        <v>84.49738000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05105</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.84379</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +532,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.72378</v>
+        <v>16.87404</v>
       </c>
       <c r="D4" t="n">
-        <v>16.90957</v>
+        <v>16.36939</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75256</v>
+        <v>16.54947</v>
       </c>
       <c r="F4" t="n">
-        <v>42.99962</v>
+        <v>55.92017</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05047</v>
+        <v>42.14742</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83649</v>
+        <v>84.65929</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05129</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.80353</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +563,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.75073</v>
+        <v>16.97138</v>
       </c>
       <c r="D5" t="n">
-        <v>16.76234</v>
+        <v>16.59246</v>
       </c>
       <c r="E5" t="n">
-        <v>16.45798</v>
+        <v>16.66906</v>
       </c>
       <c r="F5" t="n">
-        <v>41.48551</v>
+        <v>55.29481</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05024</v>
+        <v>41.64376</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84462</v>
+        <v>84.39887</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.81134</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +594,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.69641</v>
+        <v>16.89919</v>
       </c>
       <c r="D6" t="n">
-        <v>16.20482</v>
+        <v>16.41482</v>
       </c>
       <c r="E6" t="n">
-        <v>16.73486</v>
+        <v>16.89193</v>
       </c>
       <c r="F6" t="n">
-        <v>42.64986</v>
+        <v>56.24372</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04954</v>
+        <v>42.10334</v>
       </c>
       <c r="H6" t="n">
-        <v>1.80169</v>
+        <v>85.9937</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.83067</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +625,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.88976</v>
+        <v>16.91732</v>
       </c>
       <c r="D7" t="n">
-        <v>16.41938</v>
+        <v>16.54561</v>
       </c>
       <c r="E7" t="n">
-        <v>16.8882</v>
+        <v>16.58654</v>
       </c>
       <c r="F7" t="n">
-        <v>41.83729</v>
+        <v>56.19857</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05035</v>
+        <v>42.45467</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85208</v>
+        <v>82.96795</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05189</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.82307</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +656,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.86017</v>
+        <v>16.69198</v>
       </c>
       <c r="D8" t="n">
-        <v>16.32355</v>
+        <v>16.59803</v>
       </c>
       <c r="E8" t="n">
-        <v>16.55839</v>
+        <v>16.66341</v>
       </c>
       <c r="F8" t="n">
-        <v>43.42387</v>
+        <v>55.32975</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05118</v>
+        <v>42.2634</v>
       </c>
       <c r="H8" t="n">
-        <v>1.86312</v>
+        <v>83.51018999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05133</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.8052</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +687,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.78428</v>
+        <v>17.11582</v>
       </c>
       <c r="D9" t="n">
-        <v>16.91276</v>
+        <v>16.3505</v>
       </c>
       <c r="E9" t="n">
-        <v>16.46534</v>
+        <v>16.66323</v>
       </c>
       <c r="F9" t="n">
-        <v>42.18899</v>
+        <v>56.48798</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04925</v>
+        <v>42.85852</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81575</v>
+        <v>83.95676</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.80197</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +718,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.75967</v>
+        <v>16.63123</v>
       </c>
       <c r="D10" t="n">
-        <v>16.24079</v>
+        <v>16.31282</v>
       </c>
       <c r="E10" t="n">
-        <v>16.69742</v>
+        <v>16.51597</v>
       </c>
       <c r="F10" t="n">
-        <v>42.41388</v>
+        <v>56.6881</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05049</v>
+        <v>42.73598</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83561</v>
+        <v>86.26103000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05036</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.81282</v>
       </c>
     </row>
     <row r="11">
@@ -696,15 +760,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -718,26 +792,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.58017</v>
+        <v>16.9825</v>
       </c>
       <c r="D12" t="n">
-        <v>16.89261</v>
+        <v>16.52392</v>
       </c>
       <c r="E12" t="n">
-        <v>16.79947</v>
+        <v>16.56484</v>
       </c>
       <c r="F12" t="n">
-        <v>42.33182</v>
+        <v>56.93115</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05135</v>
+        <v>42.00409</v>
       </c>
       <c r="H12" t="n">
-        <v>1.79072</v>
+        <v>85.58008</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.81337</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +827,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.85864</v>
+        <v>17.0107</v>
       </c>
       <c r="D13" t="n">
-        <v>16.4678</v>
+        <v>16.33235</v>
       </c>
       <c r="E13" t="n">
-        <v>16.81679</v>
+        <v>16.93919</v>
       </c>
       <c r="F13" t="n">
-        <v>42.25863</v>
+        <v>56.23394</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05121</v>
+        <v>42.48532</v>
       </c>
       <c r="H13" t="n">
-        <v>1.87897</v>
+        <v>85.46665</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05072</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.83514</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +858,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.80084</v>
+        <v>16.89295</v>
       </c>
       <c r="D14" t="n">
-        <v>16.54658</v>
+        <v>16.74347</v>
       </c>
       <c r="E14" t="n">
-        <v>16.44956</v>
+        <v>16.86366</v>
       </c>
       <c r="F14" t="n">
-        <v>42.45832</v>
+        <v>56.0727</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05085</v>
+        <v>41.95373</v>
       </c>
       <c r="H14" t="n">
-        <v>1.81952</v>
+        <v>84.89532</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.04974</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.83046</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +889,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.71741</v>
+        <v>16.92161</v>
       </c>
       <c r="D15" t="n">
-        <v>16.2251</v>
+        <v>16.37428</v>
       </c>
       <c r="E15" t="n">
-        <v>17.08077</v>
+        <v>16.80475</v>
       </c>
       <c r="F15" t="n">
-        <v>42.46674</v>
+        <v>56.36836</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05018</v>
+        <v>42.83625</v>
       </c>
       <c r="H15" t="n">
-        <v>1.81347</v>
+        <v>84.10886000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05066</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.86162</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +920,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.77489</v>
+        <v>16.97305</v>
       </c>
       <c r="D16" t="n">
-        <v>16.47905</v>
+        <v>16.4903</v>
       </c>
       <c r="E16" t="n">
-        <v>16.42587</v>
+        <v>16.89543</v>
       </c>
       <c r="F16" t="n">
-        <v>42.39387</v>
+        <v>56.05964</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04998</v>
+        <v>42.48022</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81906</v>
+        <v>85.63267999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05081</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.81408</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +951,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.05298</v>
+        <v>16.89527</v>
       </c>
       <c r="D17" t="n">
-        <v>16.52555</v>
+        <v>16.46583</v>
       </c>
       <c r="E17" t="n">
-        <v>17.04655</v>
+        <v>16.70762</v>
       </c>
       <c r="F17" t="n">
-        <v>42.71603</v>
+        <v>57.26241</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05023</v>
+        <v>42.60333</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8401</v>
+        <v>84.70144999999999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05088</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.82806</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +982,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.98909</v>
+        <v>17.20349</v>
       </c>
       <c r="D18" t="n">
-        <v>16.40729</v>
+        <v>16.41534</v>
       </c>
       <c r="E18" t="n">
-        <v>16.64717</v>
+        <v>16.98736</v>
       </c>
       <c r="F18" t="n">
-        <v>42.1575</v>
+        <v>56.45582</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05033</v>
+        <v>41.97825</v>
       </c>
       <c r="H18" t="n">
-        <v>1.85417</v>
+        <v>83.85711999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.78426</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +1013,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.32256</v>
+        <v>16.89294</v>
       </c>
       <c r="D19" t="n">
-        <v>16.40998</v>
+        <v>16.72501</v>
       </c>
       <c r="E19" t="n">
-        <v>16.32927</v>
+        <v>16.73987</v>
       </c>
       <c r="F19" t="n">
-        <v>43.02128</v>
+        <v>54.60616</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05191</v>
+        <v>42.32995</v>
       </c>
       <c r="H19" t="n">
-        <v>1.84537</v>
+        <v>86.27557</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05113</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.79272</v>
       </c>
     </row>
     <row r="20">
@@ -922,33 +1044,54 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.64211</v>
+        <v>16.81271</v>
       </c>
       <c r="D20" t="n">
-        <v>16.58676</v>
+        <v>16.22637</v>
       </c>
       <c r="E20" t="n">
-        <v>16.86697</v>
+        <v>16.67368</v>
       </c>
       <c r="F20" t="n">
-        <v>42.76039</v>
+        <v>55.97234</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05019</v>
+        <v>42.71546</v>
       </c>
       <c r="H20" t="n">
-        <v>1.85355</v>
+        <v>86.5676</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.04907</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.81294</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -960,14 +1103,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.61333</v>
+        <v>16.56879</v>
       </c>
       <c r="D22" t="n">
-        <v>1.08936</v>
+        <v>15.61485</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.42088</v>
+      </c>
+      <c r="F22" t="n">
+        <v>21.41694</v>
+      </c>
+      <c r="G22" t="n">
+        <v>34.53068</v>
       </c>
     </row>
     <row r="23">
@@ -977,10 +1129,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.59474</v>
+        <v>16.92974</v>
       </c>
       <c r="D23" t="n">
-        <v>1.11696</v>
+        <v>16.13</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.53105</v>
+      </c>
+      <c r="F23" t="n">
+        <v>21.89464</v>
+      </c>
+      <c r="G23" t="n">
+        <v>34.10069</v>
       </c>
     </row>
     <row r="24">
@@ -990,10 +1151,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.59214</v>
+        <v>16.84135</v>
       </c>
       <c r="D24" t="n">
-        <v>1.12213</v>
+        <v>16.03776</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.14285</v>
+      </c>
+      <c r="F24" t="n">
+        <v>21.67976</v>
+      </c>
+      <c r="G24" t="n">
+        <v>34.06139</v>
       </c>
     </row>
     <row r="25">
@@ -1003,10 +1173,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.60351</v>
+        <v>16.59671</v>
       </c>
       <c r="D25" t="n">
-        <v>1.10606</v>
+        <v>15.96646</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.21132</v>
+      </c>
+      <c r="F25" t="n">
+        <v>22.38955</v>
+      </c>
+      <c r="G25" t="n">
+        <v>34.85497</v>
       </c>
     </row>
     <row r="26">
@@ -1016,10 +1195,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6039</v>
+        <v>17.07281</v>
       </c>
       <c r="D26" t="n">
-        <v>1.10419</v>
+        <v>16.33104</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.40702</v>
+      </c>
+      <c r="F26" t="n">
+        <v>21.7493</v>
+      </c>
+      <c r="G26" t="n">
+        <v>34.17132</v>
       </c>
     </row>
     <row r="27">
@@ -1029,10 +1217,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.60347</v>
+        <v>16.57949</v>
       </c>
       <c r="D27" t="n">
-        <v>1.11407</v>
+        <v>15.87383</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.36163</v>
+      </c>
+      <c r="F27" t="n">
+        <v>21.53971</v>
+      </c>
+      <c r="G27" t="n">
+        <v>33.65766</v>
       </c>
     </row>
     <row r="28">
@@ -1042,10 +1239,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.61089</v>
+        <v>16.50943</v>
       </c>
       <c r="D28" t="n">
-        <v>1.13088</v>
+        <v>15.79061</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.4543</v>
+      </c>
+      <c r="F28" t="n">
+        <v>21.93378</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34.33584</v>
       </c>
     </row>
     <row r="29">
@@ -1055,10 +1261,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.60836</v>
+        <v>16.86202</v>
       </c>
       <c r="D29" t="n">
-        <v>1.13123</v>
+        <v>16.28662</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.31526</v>
+      </c>
+      <c r="F29" t="n">
+        <v>21.52448</v>
+      </c>
+      <c r="G29" t="n">
+        <v>34.76095</v>
       </c>
     </row>
     <row r="30">
@@ -1068,10 +1283,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.5938600000000001</v>
+        <v>16.77359</v>
       </c>
       <c r="D30" t="n">
-        <v>1.12675</v>
+        <v>15.9657</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.63629</v>
+      </c>
+      <c r="F30" t="n">
+        <v>22.21085</v>
+      </c>
+      <c r="G30" t="n">
+        <v>34.15956</v>
       </c>
     </row>
     <row r="31">
@@ -1128,28 +1352,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.73502</v>
+        <v>0.749</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08074000000000001</v>
+        <v>0.08101999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>0.62033</v>
+        <v>0.61254</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9573199999999999</v>
+        <v>0.96914</v>
       </c>
       <c r="G32" t="n">
-        <v>0.10975</v>
+        <v>0.10858</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00759</v>
+        <v>0.00754</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09203</v>
+        <v>0.09508</v>
       </c>
       <c r="J32" t="n">
-        <v>0.12527</v>
+        <v>0.1251</v>
       </c>
     </row>
     <row r="33">
@@ -1159,28 +1383,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.75493</v>
+        <v>0.75242</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07973</v>
+        <v>0.08223</v>
       </c>
       <c r="E33" t="n">
-        <v>0.59785</v>
+        <v>0.60959</v>
       </c>
       <c r="F33" t="n">
-        <v>0.96855</v>
+        <v>0.95932</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1099</v>
+        <v>0.10997</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00774</v>
+        <v>0.00747</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09494</v>
+        <v>0.09364</v>
       </c>
       <c r="J33" t="n">
-        <v>0.128</v>
+        <v>0.12604</v>
       </c>
     </row>
     <row r="34">
@@ -1190,28 +1414,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.7349599999999999</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08013000000000001</v>
+        <v>0.08101999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.60056</v>
+        <v>0.61776</v>
       </c>
       <c r="F34" t="n">
-        <v>0.96854</v>
+        <v>0.95728</v>
       </c>
       <c r="G34" t="n">
-        <v>0.10977</v>
+        <v>0.10777</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00765</v>
+        <v>0.0076</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09214</v>
+        <v>0.09235</v>
       </c>
       <c r="J34" t="n">
-        <v>0.12793</v>
+        <v>0.12872</v>
       </c>
     </row>
     <row r="35">
@@ -1221,28 +1445,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.76345</v>
+        <v>0.74213</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08176</v>
+        <v>0.08061</v>
       </c>
       <c r="E35" t="n">
-        <v>0.60958</v>
+        <v>0.6170099999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.93689</v>
+        <v>0.95956</v>
       </c>
       <c r="G35" t="n">
-        <v>0.11117</v>
+        <v>0.1095</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00778</v>
+        <v>0.00766</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09313</v>
+        <v>0.09325</v>
       </c>
       <c r="J35" t="n">
-        <v>0.12525</v>
+        <v>0.12695</v>
       </c>
     </row>
     <row r="36">
@@ -1252,28 +1476,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.75764</v>
+        <v>0.75296</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08198</v>
+        <v>0.08171</v>
       </c>
       <c r="E36" t="n">
-        <v>0.61084</v>
+        <v>0.61671</v>
       </c>
       <c r="F36" t="n">
-        <v>0.94883</v>
+        <v>0.94298</v>
       </c>
       <c r="G36" t="n">
-        <v>0.10812</v>
+        <v>0.10738</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00752</v>
+        <v>0.00749</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09301</v>
+        <v>0.09474</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1266</v>
+        <v>0.12618</v>
       </c>
     </row>
     <row r="37">
@@ -1283,28 +1507,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.76119</v>
+        <v>0.72383</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08067000000000001</v>
+        <v>0.07964</v>
       </c>
       <c r="E37" t="n">
-        <v>0.60381</v>
+        <v>0.59649</v>
       </c>
       <c r="F37" t="n">
-        <v>0.94809</v>
+        <v>0.95202</v>
       </c>
       <c r="G37" t="n">
-        <v>0.11223</v>
+        <v>0.10869</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00761</v>
+        <v>0.00754</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09339</v>
+        <v>0.09322</v>
       </c>
       <c r="J37" t="n">
-        <v>0.12545</v>
+        <v>0.12709</v>
       </c>
     </row>
     <row r="38">
@@ -1314,28 +1538,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.74096</v>
+        <v>0.7436199999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08005</v>
+        <v>0.08105999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.59987</v>
       </c>
       <c r="F38" t="n">
-        <v>0.95997</v>
+        <v>0.952</v>
       </c>
       <c r="G38" t="n">
-        <v>0.10775</v>
+        <v>0.10938</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00768</v>
+        <v>0.00765</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09414</v>
+        <v>0.09598</v>
       </c>
       <c r="J38" t="n">
-        <v>0.12601</v>
+        <v>0.12783</v>
       </c>
     </row>
     <row r="39">
@@ -1345,28 +1569,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.74769</v>
+        <v>0.7462</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08035</v>
+        <v>0.08153000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>0.62199</v>
+        <v>0.59038</v>
       </c>
       <c r="F39" t="n">
-        <v>0.94737</v>
+        <v>0.96643</v>
       </c>
       <c r="G39" t="n">
-        <v>0.10944</v>
+        <v>0.10803</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00748</v>
+        <v>0.0076</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09497</v>
+        <v>0.09494</v>
       </c>
       <c r="J39" t="n">
-        <v>0.12522</v>
+        <v>0.12618</v>
       </c>
     </row>
     <row r="40">
@@ -1376,28 +1600,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.74775</v>
+        <v>0.74669</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08085000000000001</v>
+        <v>0.08083</v>
       </c>
       <c r="E40" t="n">
-        <v>0.61966</v>
+        <v>0.60799</v>
       </c>
       <c r="F40" t="n">
-        <v>0.95905</v>
+        <v>0.9581499999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0.10931</v>
+        <v>0.11017</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00757</v>
+        <v>0.00749</v>
       </c>
       <c r="I40" t="n">
-        <v>0.09361</v>
+        <v>0.09281</v>
       </c>
       <c r="J40" t="n">
-        <v>0.12777</v>
+        <v>0.12607</v>
       </c>
     </row>
   </sheetData>
